--- a/测试用例/国药总医院第二院区/处理后表格/6月__国药总医院第二院区5.26-6.25账单.xlsx
+++ b/测试用例/国药总医院第二院区/处理后表格/6月__国药总医院第二院区5.26-6.25账单.xlsx
@@ -3368,10 +3368,10 @@
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>66</v>
+        <v>16.5</v>
       </c>
       <c r="K45" t="n">
-        <v>66</v>
+        <v>16.5</v>
       </c>
     </row>
   </sheetData>
